--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/125.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/125.xlsx
@@ -426,13 +426,13 @@
         <v>-17.50839089051365</v>
       </c>
       <c r="E2">
-        <v>-8.880697355195778</v>
+        <v>-13.02421031594809</v>
       </c>
       <c r="F2">
-        <v>-0.8866407117317502</v>
+        <v>-0.8521773143056796</v>
       </c>
       <c r="G2">
-        <v>-7.834899733059008</v>
+        <v>-7.412819797759838</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.41613855398871</v>
       </c>
       <c r="E3">
-        <v>-8.964120903365082</v>
+        <v>-12.15851552532377</v>
       </c>
       <c r="F3">
-        <v>-0.4774628345471148</v>
+        <v>-1.104054848637911</v>
       </c>
       <c r="G3">
-        <v>-7.488579922345856</v>
+        <v>-7.099938915958987</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.32653698089851</v>
       </c>
       <c r="E4">
-        <v>-10.06896440633447</v>
+        <v>-12.18504785453471</v>
       </c>
       <c r="F4">
-        <v>-0.563643694032167</v>
+        <v>-1.476675215602199</v>
       </c>
       <c r="G4">
-        <v>-7.319121234908334</v>
+        <v>-6.54558965837704</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.23264860646408</v>
       </c>
       <c r="E5">
-        <v>-10.84204284655392</v>
+        <v>-13.63207643894569</v>
       </c>
       <c r="F5">
-        <v>-0.8633039452600825</v>
+        <v>-0.9595585807305794</v>
       </c>
       <c r="G5">
-        <v>-5.997491127865834</v>
+        <v>-7.81196727558005</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.12578458333141</v>
       </c>
       <c r="E6">
-        <v>-11.58378877511429</v>
+        <v>-15.03769212855653</v>
       </c>
       <c r="F6">
-        <v>-0.2640165775003634</v>
+        <v>-0.5158833430563586</v>
       </c>
       <c r="G6">
-        <v>-5.332308768448964</v>
+        <v>-6.289861093698597</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.00680356822714</v>
       </c>
       <c r="E7">
-        <v>-12.91352988272662</v>
+        <v>-15.97295333688669</v>
       </c>
       <c r="F7">
-        <v>-0.6374785657458953</v>
+        <v>-0.4215935950653021</v>
       </c>
       <c r="G7">
-        <v>-5.378856177491246</v>
+        <v>-4.003377943436701</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.88010417641645</v>
       </c>
       <c r="E8">
-        <v>-12.65814659106405</v>
+        <v>-15.06747137363097</v>
       </c>
       <c r="F8">
-        <v>-0.3280344671235148</v>
+        <v>-0.7299989209645721</v>
       </c>
       <c r="G8">
-        <v>-4.083587404457327</v>
+        <v>-5.073856789876182</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.74321087545349</v>
       </c>
       <c r="E9">
-        <v>-13.44689807982404</v>
+        <v>-17.28048227949139</v>
       </c>
       <c r="F9">
-        <v>-0.7411396341648226</v>
+        <v>-0.6879004611868984</v>
       </c>
       <c r="G9">
-        <v>-4.401839645950989</v>
+        <v>-4.151151037587852</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.59264951621871</v>
       </c>
       <c r="E10">
-        <v>-13.64770873122017</v>
+        <v>-17.66787058847755</v>
       </c>
       <c r="F10">
-        <v>-0.3740991500257925</v>
+        <v>-0.7423705881253827</v>
       </c>
       <c r="G10">
-        <v>-3.530117514253311</v>
+        <v>-3.493092210176536</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.42379366116444</v>
       </c>
       <c r="E11">
-        <v>-14.61302995001324</v>
+        <v>-18.20446758754244</v>
       </c>
       <c r="F11">
-        <v>-0.1043023720362019</v>
+        <v>0.02358595781240257</v>
       </c>
       <c r="G11">
-        <v>-2.949974573992569</v>
+        <v>-3.998429861325058</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.22649832205579</v>
       </c>
       <c r="E12">
-        <v>-15.74930559106987</v>
+        <v>-19.7269903621353</v>
       </c>
       <c r="F12">
-        <v>-0.1772401218526984</v>
+        <v>0.2441073008464646</v>
       </c>
       <c r="G12">
-        <v>-2.511436031351223</v>
+        <v>-3.421843765234754</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.99781626291867</v>
       </c>
       <c r="E13">
-        <v>-16.3419560414017</v>
+        <v>-18.31520689092601</v>
       </c>
       <c r="F13">
-        <v>-0.2077687741154713</v>
+        <v>0.8246669383636924</v>
       </c>
       <c r="G13">
-        <v>-1.732264034959243</v>
+        <v>-2.161241097976367</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.7477324201508</v>
       </c>
       <c r="E14">
-        <v>-16.69877262236208</v>
+        <v>-20.4621383040665</v>
       </c>
       <c r="F14">
-        <v>-0.1856646183391693</v>
+        <v>0.8088633450530835</v>
       </c>
       <c r="G14">
-        <v>-1.185494399179613</v>
+        <v>-2.760746526659392</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.47902704314441</v>
       </c>
       <c r="E15">
-        <v>-17.83048356161898</v>
+        <v>-21.43174798774483</v>
       </c>
       <c r="F15">
-        <v>-0.3405974871543721</v>
+        <v>0.02229370466403534</v>
       </c>
       <c r="G15">
-        <v>-1.081476394523657</v>
+        <v>-2.054778583258624</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.19592874161868</v>
       </c>
       <c r="E16">
-        <v>-19.05868722503132</v>
+        <v>-22.60751192214834</v>
       </c>
       <c r="F16">
-        <v>0.02708829519143888</v>
+        <v>0.6117665754353859</v>
       </c>
       <c r="G16">
-        <v>-0.702843113893093</v>
+        <v>-2.357202211949524</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.90309753381972</v>
       </c>
       <c r="E17">
-        <v>-20.21568969162106</v>
+        <v>-22.8013124957806</v>
       </c>
       <c r="F17">
-        <v>-0.03524552350182112</v>
+        <v>1.309795337608806</v>
       </c>
       <c r="G17">
-        <v>-0.6369824347519186</v>
+        <v>-1.342192415972455</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.6001666196004</v>
       </c>
       <c r="E18">
-        <v>-21.25487937842724</v>
+        <v>-23.82366078775226</v>
       </c>
       <c r="F18">
-        <v>0.3013126969489928</v>
+        <v>0.8744153711062196</v>
       </c>
       <c r="G18">
-        <v>0.226845077873735</v>
+        <v>-0.1611495278659243</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.28630285780575</v>
       </c>
       <c r="E19">
-        <v>-20.556307921056</v>
+        <v>-23.33424143089928</v>
       </c>
       <c r="F19">
-        <v>0.1539585615020028</v>
+        <v>0.79737554591106</v>
       </c>
       <c r="G19">
-        <v>0.8264423807604245</v>
+        <v>-0.2397085344421497</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.9686321119216</v>
       </c>
       <c r="E20">
-        <v>-21.99109151175024</v>
+        <v>-24.54616523025405</v>
       </c>
       <c r="F20">
-        <v>0.3655956641410401</v>
+        <v>1.14952943945438</v>
       </c>
       <c r="G20">
-        <v>1.862579962358758</v>
+        <v>1.130578807105355</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.6498303402065</v>
       </c>
       <c r="E21">
-        <v>-22.09832124777787</v>
+        <v>-26.22387428061576</v>
       </c>
       <c r="F21">
-        <v>0.5346803616656696</v>
+        <v>1.403594692097405</v>
       </c>
       <c r="G21">
-        <v>1.787814047905251</v>
+        <v>1.075562565218146</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.33007413304419</v>
       </c>
       <c r="E22">
-        <v>-22.63811082101817</v>
+        <v>-27.38865213707667</v>
       </c>
       <c r="F22">
-        <v>0.900298538974093</v>
+        <v>0.789888761324558</v>
       </c>
       <c r="G22">
-        <v>1.781002231947844</v>
+        <v>1.39114389236242</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.01056175513061</v>
       </c>
       <c r="E23">
-        <v>-23.17127070831124</v>
+        <v>-27.62945827090855</v>
       </c>
       <c r="F23">
-        <v>0.9262280954165231</v>
+        <v>0.9252589055552476</v>
       </c>
       <c r="G23">
-        <v>2.097590894110867</v>
+        <v>3.092936329282184</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.69170272620298</v>
       </c>
       <c r="E24">
-        <v>-23.97587185609808</v>
+        <v>-28.6574716838638</v>
       </c>
       <c r="F24">
-        <v>0.9890796437365328</v>
+        <v>1.335638743841345</v>
       </c>
       <c r="G24">
-        <v>2.69119996765157</v>
+        <v>3.318904214416463</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.37357773533243</v>
       </c>
       <c r="E25">
-        <v>-24.36858565051726</v>
+        <v>-28.03986028480169</v>
       </c>
       <c r="F25">
-        <v>0.9833506547787714</v>
+        <v>1.325038954555123</v>
       </c>
       <c r="G25">
-        <v>2.219521087259833</v>
+        <v>2.439835427647188</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.06502996344434</v>
       </c>
       <c r="E26">
-        <v>-24.28154838008984</v>
+        <v>-26.67807116663708</v>
       </c>
       <c r="F26">
-        <v>0.7606772132322362</v>
+        <v>1.18234438574888</v>
       </c>
       <c r="G26">
-        <v>3.411424818728126</v>
+        <v>2.375992699765073</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.77714089173259</v>
       </c>
       <c r="E27">
-        <v>-24.81294216251991</v>
+        <v>-27.6209311543521</v>
       </c>
       <c r="F27">
-        <v>0.9729712112216936</v>
+        <v>1.085198426952971</v>
       </c>
       <c r="G27">
-        <v>3.156592027535411</v>
+        <v>4.996458267676609</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.51502504053676</v>
       </c>
       <c r="E28">
-        <v>-24.46539083937923</v>
+        <v>-27.18678182276274</v>
       </c>
       <c r="F28">
-        <v>0.8077334519156649</v>
+        <v>0.9044635702753688</v>
       </c>
       <c r="G28">
-        <v>3.368719720131952</v>
+        <v>3.845701054563753</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.28243810824053</v>
       </c>
       <c r="E29">
-        <v>-24.53785095197596</v>
+        <v>-29.17039382081659</v>
       </c>
       <c r="F29">
-        <v>0.8375778727037255</v>
+        <v>0.6377276098391225</v>
       </c>
       <c r="G29">
-        <v>3.19559918943409</v>
+        <v>2.8955938210325</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.08118644397132</v>
       </c>
       <c r="E30">
-        <v>-25.1149732649355</v>
+        <v>-28.80191641928646</v>
       </c>
       <c r="F30">
-        <v>0.8374619012673337</v>
+        <v>1.376227089843715</v>
       </c>
       <c r="G30">
-        <v>3.143119331812331</v>
+        <v>4.072400652105788</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.90783906555805</v>
       </c>
       <c r="E31">
-        <v>-24.10428579353359</v>
+        <v>-27.84213805267878</v>
       </c>
       <c r="F31">
-        <v>0.6705342724595941</v>
+        <v>0.911251212773908</v>
       </c>
       <c r="G31">
-        <v>3.597988514155033</v>
+        <v>3.08107799456635</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.76278651298522</v>
       </c>
       <c r="E32">
-        <v>-24.17368012922713</v>
+        <v>-26.65271624066813</v>
       </c>
       <c r="F32">
-        <v>0.9423680058926687</v>
+        <v>0.8156277932643443</v>
       </c>
       <c r="G32">
-        <v>3.483047322927685</v>
+        <v>2.908708863605601</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.65285316367077</v>
       </c>
       <c r="E33">
-        <v>-24.15571114436469</v>
+        <v>-27.38426404576323</v>
       </c>
       <c r="F33">
-        <v>0.9782810462736384</v>
+        <v>0.8633964279141806</v>
       </c>
       <c r="G33">
-        <v>2.922447338274996</v>
+        <v>2.521416439279662</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.57682201286292</v>
       </c>
       <c r="E34">
-        <v>-22.82217517553394</v>
+        <v>-27.61641173729245</v>
       </c>
       <c r="F34">
-        <v>0.8229439341658695</v>
+        <v>0.8971109812081204</v>
       </c>
       <c r="G34">
-        <v>2.609261302869117</v>
+        <v>2.32518954636019</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.53227615557502</v>
       </c>
       <c r="E35">
-        <v>-22.24901527733112</v>
+        <v>-26.34832127482055</v>
       </c>
       <c r="F35">
-        <v>0.9074473496602526</v>
+        <v>0.7686195998902779</v>
       </c>
       <c r="G35">
-        <v>2.440862449995295</v>
+        <v>3.080812215620035</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.51552416565719</v>
       </c>
       <c r="E36">
-        <v>-22.09976130251231</v>
+        <v>-23.44291122166135</v>
       </c>
       <c r="F36">
-        <v>0.8517164475347075</v>
+        <v>0.9993398023876074</v>
       </c>
       <c r="G36">
-        <v>3.260396752790004</v>
+        <v>1.754998551089244</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.51781528085177</v>
       </c>
       <c r="E37">
-        <v>-21.42873202405572</v>
+        <v>-24.92258104671962</v>
       </c>
       <c r="F37">
-        <v>0.6248862583609245</v>
+        <v>1.540329985807908</v>
       </c>
       <c r="G37">
-        <v>2.144814234794395</v>
+        <v>1.828071355218078</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.53430864401121</v>
       </c>
       <c r="E38">
-        <v>-20.48282890180754</v>
+        <v>-24.2691267758868</v>
       </c>
       <c r="F38">
-        <v>0.7450475770762152</v>
+        <v>1.286009596004821</v>
       </c>
       <c r="G38">
-        <v>1.744009740086664</v>
+        <v>2.154867897652534</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.56764582272923</v>
       </c>
       <c r="E39">
-        <v>-21.01848397827884</v>
+        <v>-22.23677481208838</v>
       </c>
       <c r="F39">
-        <v>0.8239677962757297</v>
+        <v>1.183944791571088</v>
       </c>
       <c r="G39">
-        <v>2.500150842352901</v>
+        <v>0.6669028260971036</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.61776849330795</v>
       </c>
       <c r="E40">
-        <v>-19.39546530850776</v>
+        <v>-22.91184801783383</v>
       </c>
       <c r="F40">
-        <v>1.089220979060965</v>
+        <v>0.9783423454614456</v>
       </c>
       <c r="G40">
-        <v>1.814362411542718</v>
+        <v>1.447649808837617</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.68352318065175</v>
       </c>
       <c r="E41">
-        <v>-19.8461345132771</v>
+        <v>-22.9445390716952</v>
       </c>
       <c r="F41">
-        <v>1.012485993070036</v>
+        <v>1.049563718019341</v>
       </c>
       <c r="G41">
-        <v>1.302422942616594</v>
+        <v>1.946969699646117</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.76387243970371</v>
       </c>
       <c r="E42">
-        <v>-18.15233579476614</v>
+        <v>-20.9153208119101</v>
       </c>
       <c r="F42">
-        <v>0.9330074542410343</v>
+        <v>1.461355094359809</v>
       </c>
       <c r="G42">
-        <v>1.66603150972646</v>
+        <v>1.182215390786337</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.85511494612751</v>
       </c>
       <c r="E43">
-        <v>-18.20357547816293</v>
+        <v>-21.51490888442169</v>
       </c>
       <c r="F43">
-        <v>0.8694783013855345</v>
+        <v>1.62132940718845</v>
       </c>
       <c r="G43">
-        <v>1.71318594475724</v>
+        <v>0.6333260858793058</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.95360982182879</v>
       </c>
       <c r="E44">
-        <v>-17.24562661505435</v>
+        <v>-19.98465147622372</v>
       </c>
       <c r="F44">
-        <v>1.12879871683192</v>
+        <v>1.041036503974923</v>
       </c>
       <c r="G44">
-        <v>1.538296835638837</v>
+        <v>0.3851476120091453</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.0629389624292</v>
       </c>
       <c r="E45">
-        <v>-16.26680148677041</v>
+        <v>-18.73080306450595</v>
       </c>
       <c r="F45">
-        <v>1.309792024139195</v>
+        <v>1.60629785229725</v>
       </c>
       <c r="G45">
-        <v>0.5619693606260616</v>
+        <v>-1.056270050504002</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.18646002973648</v>
       </c>
       <c r="E46">
-        <v>-15.73999957698411</v>
+        <v>-19.09750983269908</v>
       </c>
       <c r="F46">
-        <v>1.366122664264367</v>
+        <v>1.397105261863874</v>
       </c>
       <c r="G46">
-        <v>1.165153038677224</v>
+        <v>0.9881114482158251</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.32372176624826</v>
       </c>
       <c r="E47">
-        <v>-15.48995988465059</v>
+        <v>-18.92703542868033</v>
       </c>
       <c r="F47">
-        <v>1.136315322644923</v>
+        <v>1.274457184205379</v>
       </c>
       <c r="G47">
-        <v>0.7709930176273683</v>
+        <v>-0.8674390309795182</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.47338636901506</v>
       </c>
       <c r="E48">
-        <v>-14.21037162667321</v>
+        <v>-17.20757384796789</v>
       </c>
       <c r="F48">
-        <v>1.507355992972071</v>
+        <v>1.945777724577738</v>
       </c>
       <c r="G48">
-        <v>0.1354696198863185</v>
+        <v>-0.09299855607625758</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.63201813420372</v>
       </c>
       <c r="E49">
-        <v>-12.53103685414275</v>
+        <v>-18.97034122561568</v>
       </c>
       <c r="F49">
-        <v>1.339182499590521</v>
+        <v>1.806935064194513</v>
       </c>
       <c r="G49">
-        <v>0.2041652744548531</v>
+        <v>-2.638169932863216</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.7913405744645</v>
       </c>
       <c r="E50">
-        <v>-13.26729880067983</v>
+        <v>-15.31097194949742</v>
       </c>
       <c r="F50">
-        <v>1.616705460346023</v>
+        <v>1.65738161329309</v>
       </c>
       <c r="G50">
-        <v>-0.04317648791764902</v>
+        <v>-1.189487645817458</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.94980678209258</v>
       </c>
       <c r="E51">
-        <v>-12.86299211280101</v>
+        <v>-15.35108517225736</v>
       </c>
       <c r="F51">
-        <v>1.531951877895994</v>
+        <v>1.525187429684734</v>
       </c>
       <c r="G51">
-        <v>-0.2612366290936665</v>
+        <v>-2.431997657397067</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.10914544788921</v>
       </c>
       <c r="E52">
-        <v>-11.45959084697992</v>
+        <v>-14.91011595881245</v>
       </c>
       <c r="F52">
-        <v>1.301302914995306</v>
+        <v>1.907305028922118</v>
       </c>
       <c r="G52">
-        <v>-0.3600965534581763</v>
+        <v>-2.221796041855919</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.26587150535399</v>
       </c>
       <c r="E53">
-        <v>-11.02449506432296</v>
+        <v>-14.14632089030873</v>
       </c>
       <c r="F53">
-        <v>1.70895079758697</v>
+        <v>1.194446833503781</v>
       </c>
       <c r="G53">
-        <v>-0.7923942126934582</v>
+        <v>-2.426137395691898</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.41617273834042</v>
       </c>
       <c r="E54">
-        <v>-11.26725297045214</v>
+        <v>-11.83060872242836</v>
       </c>
       <c r="F54">
-        <v>1.554491754926169</v>
+        <v>1.990083783483872</v>
       </c>
       <c r="G54">
-        <v>-1.795115833930407</v>
+        <v>-1.767241856782924</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.55622600104525</v>
       </c>
       <c r="E55">
-        <v>-9.128952828770275</v>
+        <v>-12.00369152747553</v>
       </c>
       <c r="F55">
-        <v>1.429618682423755</v>
+        <v>1.225547059274485</v>
       </c>
       <c r="G55">
-        <v>-1.807948691449395</v>
+        <v>-2.044800388496352</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.67673254094807</v>
       </c>
       <c r="E56">
-        <v>-9.742434259537394</v>
+        <v>-12.50890620166726</v>
       </c>
       <c r="F56">
-        <v>1.557058037140042</v>
+        <v>1.494065666361556</v>
       </c>
       <c r="G56">
-        <v>-1.551983878818672</v>
+        <v>-3.06235641240355</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.7746184513456</v>
       </c>
       <c r="E57">
-        <v>-8.847856861692154</v>
+        <v>-11.15474303373157</v>
       </c>
       <c r="F57">
-        <v>1.687103435705536</v>
+        <v>0.7503309043712705</v>
       </c>
       <c r="G57">
-        <v>-1.914309488298795</v>
+        <v>-2.374648466981092</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.85326141105098</v>
       </c>
       <c r="E58">
-        <v>-8.538417175800022</v>
+        <v>-9.88354603809041</v>
       </c>
       <c r="F58">
-        <v>1.362603759537275</v>
+        <v>1.638055801785777</v>
       </c>
       <c r="G58">
-        <v>-2.463645039337911</v>
+        <v>-2.813088572975654</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.9123238367899</v>
       </c>
       <c r="E59">
-        <v>-8.586305788431137</v>
+        <v>-9.691094949712435</v>
       </c>
       <c r="F59">
-        <v>1.641114134236913</v>
+        <v>1.320610502419757</v>
       </c>
       <c r="G59">
-        <v>-2.553356917994689</v>
+        <v>-3.186117527182686</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.95076258190678</v>
       </c>
       <c r="E60">
-        <v>-8.95230611467907</v>
+        <v>-9.495374303100922</v>
       </c>
       <c r="F60">
-        <v>1.438005074009697</v>
+        <v>1.138749066074347</v>
       </c>
       <c r="G60">
-        <v>-2.716102226121587</v>
+        <v>-3.44550137267835</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.96755734029679</v>
       </c>
       <c r="E61">
-        <v>-8.174314280161303</v>
+        <v>-10.49495795623602</v>
       </c>
       <c r="F61">
-        <v>1.382012407784867</v>
+        <v>1.700194954139379</v>
       </c>
       <c r="G61">
-        <v>-2.840198025499786</v>
+        <v>-4.097247129809295</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.95845553968274</v>
       </c>
       <c r="E62">
-        <v>-8.274869045501623</v>
+        <v>-9.228887193171545</v>
       </c>
       <c r="F62">
-        <v>1.305711486313005</v>
+        <v>1.193439538741976</v>
       </c>
       <c r="G62">
-        <v>-3.477083130188006</v>
+        <v>-3.844041824510065</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.92001494891308</v>
       </c>
       <c r="E63">
-        <v>-7.693077875840181</v>
+        <v>-8.696121283117142</v>
       </c>
       <c r="F63">
-        <v>1.709041918001278</v>
+        <v>0.1444190824913636</v>
       </c>
       <c r="G63">
-        <v>-3.503802117346564</v>
+        <v>-4.53478818109657</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.85669044830079</v>
       </c>
       <c r="E64">
-        <v>-7.464326539816721</v>
+        <v>-10.11450726942961</v>
       </c>
       <c r="F64">
-        <v>1.199176811373766</v>
+        <v>0.812687088984406</v>
       </c>
       <c r="G64">
-        <v>-2.636759007592655</v>
+        <v>-3.555717604860098</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.77316545371774</v>
       </c>
       <c r="E65">
-        <v>-6.708451772352416</v>
+        <v>-10.23043620402598</v>
       </c>
       <c r="F65">
-        <v>0.9569522423863567</v>
+        <v>0.9672554761423769</v>
       </c>
       <c r="G65">
-        <v>-3.43226820612911</v>
+        <v>-4.832375289208849</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.67130234854611</v>
       </c>
       <c r="E66">
-        <v>-7.675117947925761</v>
+        <v>-8.935283580884237</v>
       </c>
       <c r="F66">
-        <v>1.318440179824422</v>
+        <v>0.7025291350253222</v>
       </c>
       <c r="G66">
-        <v>-3.406668115522322</v>
+        <v>-4.896428015270769</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.55304815243085</v>
       </c>
       <c r="E67">
-        <v>-6.411180096118895</v>
+        <v>-9.432242846959991</v>
       </c>
       <c r="F67">
-        <v>1.084679868958818</v>
+        <v>0.7202280329535364</v>
       </c>
       <c r="G67">
-        <v>-3.949907156903989</v>
+        <v>-4.581899960247076</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.41907244740275</v>
       </c>
       <c r="E68">
-        <v>-7.463937091052061</v>
+        <v>-8.355697778064531</v>
       </c>
       <c r="F68">
-        <v>0.9884020392010427</v>
+        <v>0.6967968325979496</v>
       </c>
       <c r="G68">
-        <v>-3.837374382301273</v>
+        <v>-4.594562194244974</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.26726360574458</v>
       </c>
       <c r="E69">
-        <v>-7.011298000089378</v>
+        <v>-8.684763870305906</v>
       </c>
       <c r="F69">
-        <v>1.300464607183673</v>
+        <v>1.172476873246732</v>
       </c>
       <c r="G69">
-        <v>-4.182755763648424</v>
+        <v>-4.900903601477851</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.10195154715812</v>
       </c>
       <c r="E70">
-        <v>-6.91921600961741</v>
+        <v>-8.071776043205624</v>
       </c>
       <c r="F70">
-        <v>1.104797599703207</v>
+        <v>0.1261179614613142</v>
       </c>
       <c r="G70">
-        <v>-3.910119064274163</v>
+        <v>-3.766946242749352</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.9321435325431</v>
       </c>
       <c r="E71">
-        <v>-7.071916153156054</v>
+        <v>-8.599257224093074</v>
       </c>
       <c r="F71">
-        <v>1.131946512962558</v>
+        <v>0.8831745280234216</v>
       </c>
       <c r="G71">
-        <v>-3.41406727013887</v>
+        <v>-4.323933602465092</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.76109284622543</v>
       </c>
       <c r="E72">
-        <v>-6.989552267904545</v>
+        <v>-7.863316799210534</v>
       </c>
       <c r="F72">
-        <v>0.9784086148536695</v>
+        <v>0.6274881603731177</v>
       </c>
       <c r="G72">
-        <v>-3.620899071138468</v>
+        <v>-4.659208821409154</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.59126134529593</v>
       </c>
       <c r="E73">
-        <v>-6.646755842471915</v>
+        <v>-10.17044750884637</v>
       </c>
       <c r="F73">
-        <v>1.253984912212592</v>
+        <v>-3.411031102253188E-05</v>
       </c>
       <c r="G73">
-        <v>-3.263026079314511</v>
+        <v>-3.945300321834529</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.42409466198144</v>
       </c>
       <c r="E74">
-        <v>-7.23621824710235</v>
+        <v>-10.54687691073396</v>
       </c>
       <c r="F74">
-        <v>1.309185659200346</v>
+        <v>0.2924127175733149</v>
       </c>
       <c r="G74">
-        <v>-3.599193790522741</v>
+        <v>-4.422832901488316</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.25585873906513</v>
       </c>
       <c r="E75">
-        <v>-8.175387528501121</v>
+        <v>-10.04791605914682</v>
       </c>
       <c r="F75">
-        <v>0.6335576083334298</v>
+        <v>0.9375170863818747</v>
       </c>
       <c r="G75">
-        <v>-3.06980150412193</v>
+        <v>-2.961573692205206</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.08620419983313</v>
       </c>
       <c r="E76">
-        <v>-8.786061305383484</v>
+        <v>-10.65565991334622</v>
       </c>
       <c r="F76">
-        <v>0.7062634152771423</v>
+        <v>0.5030856005554936</v>
       </c>
       <c r="G76">
-        <v>-2.864889217734608</v>
+        <v>-2.271513110924626</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.92162236966879</v>
       </c>
       <c r="E77">
-        <v>-9.060006812003495</v>
+        <v>-11.65181551165752</v>
       </c>
       <c r="F77">
-        <v>1.13924111631161</v>
+        <v>-0.04216984662182219</v>
       </c>
       <c r="G77">
-        <v>-2.329423390227265</v>
+        <v>-4.29824163765464</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.76298277572321</v>
       </c>
       <c r="E78">
-        <v>-9.341111836029631</v>
+        <v>-10.84346931586633</v>
       </c>
       <c r="F78">
-        <v>0.8030929377251822</v>
+        <v>0.4157210040518409</v>
       </c>
       <c r="G78">
-        <v>-2.572768624740364</v>
+        <v>-3.96437734398114</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.60994260779392</v>
       </c>
       <c r="E79">
-        <v>-9.859273417409296</v>
+        <v>-12.26883820909863</v>
       </c>
       <c r="F79">
-        <v>0.7771169927081952</v>
+        <v>-0.2346302438860509</v>
       </c>
       <c r="G79">
-        <v>-2.173210994225221</v>
+        <v>-2.839354751559009</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.46132624325133</v>
       </c>
       <c r="E80">
-        <v>-10.24797498385768</v>
+        <v>-12.55620611267738</v>
       </c>
       <c r="F80">
-        <v>0.7508362084869782</v>
+        <v>-0.2765638585505675</v>
       </c>
       <c r="G80">
-        <v>-1.585645930797015</v>
+        <v>-2.57580375468285</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.31295116334074</v>
       </c>
       <c r="E81">
-        <v>-10.40466924147109</v>
+        <v>-12.69464156309186</v>
       </c>
       <c r="F81">
-        <v>0.3394465903368681</v>
+        <v>-0.3311077101879009</v>
       </c>
       <c r="G81">
-        <v>-1.758487557662325</v>
+        <v>-2.938838108019814</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.1609255359819</v>
       </c>
       <c r="E82">
-        <v>-11.51828439859334</v>
+        <v>-13.71411880254266</v>
       </c>
       <c r="F82">
-        <v>0.4121142923800519</v>
+        <v>0.105361559449367</v>
       </c>
       <c r="G82">
-        <v>-0.874483813667646</v>
+        <v>-1.553575271275003</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.00819010818521</v>
       </c>
       <c r="E83">
-        <v>-12.51408677593204</v>
+        <v>-15.80302687822286</v>
       </c>
       <c r="F83">
-        <v>0.910891701321093</v>
+        <v>-0.01757230496309366</v>
       </c>
       <c r="G83">
-        <v>-0.7235673092625459</v>
+        <v>-1.086467132515572</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.856581850452944</v>
       </c>
       <c r="E84">
-        <v>-12.90945878459372</v>
+        <v>-15.21291690180933</v>
       </c>
       <c r="F84">
-        <v>0.8331345099551091</v>
+        <v>0.7251535055305822</v>
       </c>
       <c r="G84">
-        <v>-0.3541214489984275</v>
+        <v>-1.468217573627608</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.705087767162466</v>
       </c>
       <c r="E85">
-        <v>-14.82022574976019</v>
+        <v>-17.72476180743591</v>
       </c>
       <c r="F85">
-        <v>0.861303971854709</v>
+        <v>-0.378554938285451</v>
       </c>
       <c r="G85">
-        <v>-0.3330166319280791</v>
+        <v>0.9907331442418215</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.552513545113566</v>
       </c>
       <c r="E86">
-        <v>-14.93241416482621</v>
+        <v>-18.04981114323248</v>
       </c>
       <c r="F86">
-        <v>0.8976659873679961</v>
+        <v>0.160915190950713</v>
       </c>
       <c r="G86">
-        <v>-0.034927496917205</v>
+        <v>0.8774260013510765</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.397194618470742</v>
       </c>
       <c r="E87">
-        <v>-16.23031557169061</v>
+        <v>-18.12925416274904</v>
       </c>
       <c r="F87">
-        <v>0.9448232868745664</v>
+        <v>0.3878514111520543</v>
       </c>
       <c r="G87">
-        <v>0.3745853598092928</v>
+        <v>1.218338358934264</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.235715047102554</v>
       </c>
       <c r="E88">
-        <v>-18.31519330550399</v>
+        <v>-20.52507956429911</v>
       </c>
       <c r="F88">
-        <v>0.5286365930948443</v>
+        <v>-0.2351645408608566</v>
       </c>
       <c r="G88">
-        <v>0.5119241694014107</v>
+        <v>1.16393570547867</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.069724379276769</v>
       </c>
       <c r="E89">
-        <v>-19.27465467893113</v>
+        <v>-20.7762287327645</v>
       </c>
       <c r="F89">
-        <v>0.9960760348205774</v>
+        <v>0.4715645641441668</v>
       </c>
       <c r="G89">
-        <v>1.328534903786655</v>
+        <v>1.649477746959062</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.904176355854712</v>
       </c>
       <c r="E90">
-        <v>-20.43450102719768</v>
+        <v>-23.16499424333661</v>
       </c>
       <c r="F90">
-        <v>0.9966492650633146</v>
+        <v>0.6415778615273345</v>
       </c>
       <c r="G90">
-        <v>1.531412832807122</v>
+        <v>1.883537124458931</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.739912590857617</v>
       </c>
       <c r="E91">
-        <v>-22.6877791239343</v>
+        <v>-24.83865483793547</v>
       </c>
       <c r="F91">
-        <v>0.9762316653191124</v>
+        <v>0.3158571718073465</v>
       </c>
       <c r="G91">
-        <v>1.284202319296997</v>
+        <v>1.722235553818189</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.577545204500206</v>
       </c>
       <c r="E92">
-        <v>-24.51178958406182</v>
+        <v>-26.38768729936923</v>
       </c>
       <c r="F92">
-        <v>0.799685034230065</v>
+        <v>0.3241275919568968</v>
       </c>
       <c r="G92">
-        <v>1.122060755937037</v>
+        <v>1.848017901077942</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.417563252416555</v>
       </c>
       <c r="E93">
-        <v>-26.54449929730684</v>
+        <v>-26.71209812033072</v>
       </c>
       <c r="F93">
-        <v>0.8695362871037305</v>
+        <v>0.6292401574300387</v>
       </c>
       <c r="G93">
-        <v>1.562643499609917</v>
+        <v>1.209774370664113</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.257103566177095</v>
       </c>
       <c r="E94">
-        <v>-28.0007252124274</v>
+        <v>-29.7524612273925</v>
       </c>
       <c r="F94">
-        <v>0.7804983884464228</v>
+        <v>0.3417328843685947</v>
       </c>
       <c r="G94">
-        <v>2.07506202688372</v>
+        <v>0.644298490774089</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.096642599168439</v>
       </c>
       <c r="E95">
-        <v>-30.16877969257667</v>
+        <v>-30.98196909131905</v>
       </c>
       <c r="F95">
-        <v>0.4774691669913217</v>
+        <v>-0.4079421002671663</v>
       </c>
       <c r="G95">
-        <v>2.301978185048678</v>
+        <v>0.345221708073822</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.942633581408117</v>
       </c>
       <c r="E96">
-        <v>-32.11661448173292</v>
+        <v>-33.26458264267735</v>
       </c>
       <c r="F96">
-        <v>0.5126466171186055</v>
+        <v>0.08783910377794903</v>
       </c>
       <c r="G96">
-        <v>1.551756406475679</v>
+        <v>2.0960913758582</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.796514549055155</v>
       </c>
       <c r="E97">
-        <v>-33.50190637999734</v>
+        <v>-35.60818341773396</v>
       </c>
       <c r="F97">
-        <v>0.6018559878282926</v>
+        <v>-0.2791226854578152</v>
       </c>
       <c r="G97">
-        <v>2.110354845977107</v>
+        <v>2.903035631529321</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.659817504700586</v>
       </c>
       <c r="E98">
-        <v>-36.35461178841827</v>
+        <v>-37.16972805285091</v>
       </c>
       <c r="F98">
-        <v>0.3221875554995404</v>
+        <v>0.1437315375470401</v>
       </c>
       <c r="G98">
-        <v>1.091899767362621</v>
+        <v>2.42718303731397</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.532879251363387</v>
       </c>
       <c r="E99">
-        <v>-37.7382575863809</v>
+        <v>-39.54666971778899</v>
       </c>
       <c r="F99">
-        <v>0.5013054390068774</v>
+        <v>-0.8285555894474489</v>
       </c>
       <c r="G99">
-        <v>1.601726129604462</v>
+        <v>1.335687966786244</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.415655368918762</v>
       </c>
       <c r="E100">
-        <v>-40.73406956615522</v>
+        <v>-43.741365756013</v>
       </c>
       <c r="F100">
-        <v>0.2838159206670617</v>
+        <v>-0.3581936675246392</v>
       </c>
       <c r="G100">
-        <v>1.43362914911411</v>
+        <v>1.437487865668017</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.306648437002699</v>
       </c>
       <c r="E101">
-        <v>-42.62268097223916</v>
+        <v>-45.75206482134373</v>
       </c>
       <c r="F101">
-        <v>0.09974605682578912</v>
+        <v>-0.2745890306622935</v>
       </c>
       <c r="G101">
-        <v>1.390343274301915</v>
+        <v>-0.09884569289518806</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.214424614456378</v>
       </c>
       <c r="E102">
-        <v>-45.59212591210382</v>
+        <v>-47.63007054130171</v>
       </c>
       <c r="F102">
-        <v>-0.0416413482188361</v>
+        <v>-0.6342007159330176</v>
       </c>
       <c r="G102">
-        <v>0.6348026355810559</v>
+        <v>1.74361599349953</v>
       </c>
     </row>
   </sheetData>
